--- a/outputs/calibration_intercept.xlsx
+++ b/outputs/calibration_intercept.xlsx
@@ -416,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R127"/>
+  <dimension ref="A1:S127"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -517,6 +517,11 @@
           <t>FL</t>
         </is>
       </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>FedAvg</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -573,6 +578,9 @@
         <v>0.0080545513904137</v>
       </c>
       <c r="R3" t="n">
+        <v>0.0045180526040377</v>
+      </c>
+      <c r="S3" t="n">
         <v>0.0142850953508279</v>
       </c>
     </row>
@@ -631,6 +639,9 @@
         <v>-0.1799521487428607</v>
       </c>
       <c r="R4" t="n">
+        <v>-0.184407714946785</v>
+      </c>
+      <c r="S4" t="n">
         <v>-0.1746406721999947</v>
       </c>
     </row>
@@ -689,6 +700,9 @@
         <v>0.1765126971938495</v>
       </c>
       <c r="R5" t="n">
+        <v>0.1726847736309486</v>
+      </c>
+      <c r="S5" t="n">
         <v>0.1824518163777387</v>
       </c>
     </row>
@@ -747,6 +761,9 @@
         <v>0.1684581458034358</v>
       </c>
       <c r="R6" t="n">
+        <v>0.1681667210269109</v>
+      </c>
+      <c r="S6" t="n">
         <v>0.1681667210269108</v>
       </c>
     </row>
@@ -805,6 +822,9 @@
         <v>0.1880067001332744</v>
       </c>
       <c r="R7" t="n">
+        <v>0.1889257675508227</v>
+      </c>
+      <c r="S7" t="n">
         <v>0.1889257675508226</v>
       </c>
     </row>
@@ -906,6 +926,11 @@
           <t>FL</t>
         </is>
       </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>FedAvg</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -962,6 +987,9 @@
         <v>0.07387402827793429</v>
       </c>
       <c r="R11" t="n">
+        <v>0.07102938446371421</v>
+      </c>
+      <c r="S11" t="n">
         <v>0.0782912227976184</v>
       </c>
     </row>
@@ -1020,6 +1048,9 @@
         <v>-0.07713011869820929</v>
       </c>
       <c r="R12" t="n">
+        <v>-0.0800031588006373</v>
+      </c>
+      <c r="S12" t="n">
         <v>-0.07274132046643331</v>
       </c>
     </row>
@@ -1078,6 +1109,9 @@
         <v>0.2083113243059234</v>
       </c>
       <c r="R13" t="n">
+        <v>0.2050314087532466</v>
+      </c>
+      <c r="S13" t="n">
         <v>0.2122932470874507</v>
       </c>
     </row>
@@ -1136,6 +1170,9 @@
         <v>0.1344372960279891</v>
       </c>
       <c r="R14" t="n">
+        <v>0.1340020242895324</v>
+      </c>
+      <c r="S14" t="n">
         <v>0.1340020242898323</v>
       </c>
     </row>
@@ -1194,6 +1231,9 @@
         <v>0.1510041469761436</v>
       </c>
       <c r="R15" t="n">
+        <v>0.1510325432643515</v>
+      </c>
+      <c r="S15" t="n">
         <v>0.1510325432640517</v>
       </c>
     </row>
@@ -1295,6 +1335,11 @@
           <t>FL</t>
         </is>
       </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>FedAvg</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1351,6 +1396,9 @@
         <v>-0.0006720094231331</v>
       </c>
       <c r="R19" t="n">
+        <v>-0.00049602522865</v>
+      </c>
+      <c r="S19" t="n">
         <v>0.0042144765299398</v>
       </c>
     </row>
@@ -1409,6 +1457,9 @@
         <v>-0.180607393350117</v>
       </c>
       <c r="R20" t="n">
+        <v>-0.1810670070671679</v>
+      </c>
+      <c r="S20" t="n">
         <v>-0.176356505308576</v>
       </c>
     </row>
@@ -1467,6 +1518,9 @@
         <v>0.1722448895209282</v>
       </c>
       <c r="R21" t="n">
+        <v>0.1724063354814086</v>
+      </c>
+      <c r="S21" t="n">
         <v>0.1771168372400003</v>
       </c>
     </row>
@@ -1525,6 +1579,9 @@
         <v>0.1729168989440613</v>
       </c>
       <c r="R22" t="n">
+        <v>0.1729023607100586</v>
+      </c>
+      <c r="S22" t="n">
         <v>0.1729023607100605</v>
       </c>
     </row>
@@ -1583,6 +1640,9 @@
         <v>0.1799353839269839</v>
       </c>
       <c r="R23" t="n">
+        <v>0.1805709818385179</v>
+      </c>
+      <c r="S23" t="n">
         <v>0.1805709818385158</v>
       </c>
     </row>
@@ -1684,6 +1744,11 @@
           <t>FL</t>
         </is>
       </c>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>FedAvg</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1740,6 +1805,9 @@
         <v>0.1468550252731422</v>
       </c>
       <c r="R27" t="n">
+        <v>0.1447684683807487</v>
+      </c>
+      <c r="S27" t="n">
         <v>0.151968284372541</v>
       </c>
     </row>
@@ -1798,6 +1866,9 @@
         <v>-0.007334387602653</v>
       </c>
       <c r="R28" t="n">
+        <v>-0.0093454547812858</v>
+      </c>
+      <c r="S28" t="n">
         <v>-0.0021456387894935</v>
       </c>
     </row>
@@ -1856,6 +1927,9 @@
         <v>0.282180257752616</v>
       </c>
       <c r="R29" t="n">
+        <v>0.2794435266535747</v>
+      </c>
+      <c r="S29" t="n">
         <v>0.2866433426453672</v>
       </c>
     </row>
@@ -1914,6 +1988,9 @@
         <v>0.1353252324794738</v>
       </c>
       <c r="R30" t="n">
+        <v>0.134675058272826</v>
+      </c>
+      <c r="S30" t="n">
         <v>0.1346750582728262</v>
       </c>
     </row>
@@ -1974,6 +2051,9 @@
       <c r="R31" t="n">
         <v>0.1541139231620345</v>
       </c>
+      <c r="S31" t="n">
+        <v>0.1541139231620345</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -2073,6 +2153,11 @@
           <t>FL</t>
         </is>
       </c>
+      <c r="S34" t="inlineStr">
+        <is>
+          <t>FedAvg</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -2129,6 +2214,9 @@
         <v>0.08921745202501399</v>
       </c>
       <c r="R35" t="n">
+        <v>0.0929498475454042</v>
+      </c>
+      <c r="S35" t="n">
         <v>0.1009984988750851</v>
       </c>
     </row>
@@ -2187,6 +2275,9 @@
         <v>-0.1215318209647242</v>
       </c>
       <c r="R36" t="n">
+        <v>-0.1166425615778956</v>
+      </c>
+      <c r="S36" t="n">
         <v>-0.1085939102482148</v>
       </c>
     </row>
@@ -2245,6 +2336,9 @@
         <v>0.2684377138878843</v>
       </c>
       <c r="R37" t="n">
+        <v>0.2718252043990229</v>
+      </c>
+      <c r="S37" t="n">
         <v>0.2798738557287037</v>
       </c>
     </row>
@@ -2303,6 +2397,9 @@
         <v>0.1792202618628703</v>
       </c>
       <c r="R38" t="n">
+        <v>0.1788753568536187</v>
+      </c>
+      <c r="S38" t="n">
         <v>0.1788753568536186</v>
       </c>
     </row>
@@ -2361,6 +2458,9 @@
         <v>0.2107492729897382</v>
       </c>
       <c r="R39" t="n">
+        <v>0.2095924091232998</v>
+      </c>
+      <c r="S39" t="n">
         <v>0.2095924091232999</v>
       </c>
     </row>
@@ -2462,6 +2562,11 @@
           <t>FL</t>
         </is>
       </c>
+      <c r="S42" t="inlineStr">
+        <is>
+          <t>FedAvg</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -2518,6 +2623,9 @@
         <v>0.1950902075454667</v>
       </c>
       <c r="R43" t="n">
+        <v>0.2018153764213873</v>
+      </c>
+      <c r="S43" t="n">
         <v>0.2081172546348595</v>
       </c>
     </row>
@@ -2576,6 +2684,9 @@
         <v>-0.0267917272512502</v>
       </c>
       <c r="R44" t="n">
+        <v>-0.0198252464423345</v>
+      </c>
+      <c r="S44" t="n">
         <v>-0.0135233682288624</v>
       </c>
     </row>
@@ -2634,6 +2745,9 @@
         <v>0.3926542780128729</v>
       </c>
       <c r="R45" t="n">
+        <v>0.3994079524550838</v>
+      </c>
+      <c r="S45" t="n">
         <v>0.4057098306685615</v>
       </c>
     </row>
@@ -2692,6 +2806,9 @@
         <v>0.1975640704674062</v>
       </c>
       <c r="R46" t="n">
+        <v>0.1975925760336965</v>
+      </c>
+      <c r="S46" t="n">
         <v>0.197592576033702</v>
       </c>
     </row>
@@ -2750,6 +2867,9 @@
         <v>0.2218819347967169</v>
       </c>
       <c r="R47" t="n">
+        <v>0.2216406228637218</v>
+      </c>
+      <c r="S47" t="n">
         <v>0.2216406228637219</v>
       </c>
     </row>
@@ -2851,6 +2971,11 @@
           <t>FL</t>
         </is>
       </c>
+      <c r="S50" t="inlineStr">
+        <is>
+          <t>FedAvg</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -2907,6 +3032,9 @@
         <v>0.0123829696926012</v>
       </c>
       <c r="R51" t="n">
+        <v>0.0104712676129335</v>
+      </c>
+      <c r="S51" t="n">
         <v>0.0156344594753781</v>
       </c>
     </row>
@@ -2965,6 +3093,9 @@
         <v>-0.1593267579630683</v>
       </c>
       <c r="R52" t="n">
+        <v>-0.1615284878649865</v>
+      </c>
+      <c r="S52" t="n">
         <v>-0.1563652960025418</v>
       </c>
     </row>
@@ -3023,6 +3154,9 @@
         <v>0.1555672461249577</v>
       </c>
       <c r="R53" t="n">
+        <v>0.1537063928298329</v>
+      </c>
+      <c r="S53" t="n">
         <v>0.1588695846922775</v>
       </c>
     </row>
@@ -3083,6 +3217,9 @@
       <c r="R54" t="n">
         <v>0.1432351252168994</v>
       </c>
+      <c r="S54" t="n">
+        <v>0.1432351252168994</v>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -3139,6 +3276,9 @@
         <v>0.1717097276556695</v>
       </c>
       <c r="R55" t="n">
+        <v>0.17199975547792</v>
+      </c>
+      <c r="S55" t="n">
         <v>0.1719997554779199</v>
       </c>
     </row>
@@ -3240,6 +3380,11 @@
           <t>FL</t>
         </is>
       </c>
+      <c r="S58" t="inlineStr">
+        <is>
+          <t>FedAvg</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -3296,6 +3441,9 @@
         <v>-0.2537987696394511</v>
       </c>
       <c r="R59" t="n">
+        <v>-0.2492620641161698</v>
+      </c>
+      <c r="S59" t="n">
         <v>-0.2422975347551858</v>
       </c>
     </row>
@@ -3354,6 +3502,9 @@
         <v>-0.4063905886952158</v>
       </c>
       <c r="R60" t="n">
+        <v>-0.4017946003182774</v>
+      </c>
+      <c r="S60" t="n">
         <v>-0.3948300709572985</v>
       </c>
     </row>
@@ -3412,6 +3563,9 @@
         <v>-0.09756306689331121</v>
       </c>
       <c r="R61" t="n">
+        <v>-0.0934376250160993</v>
+      </c>
+      <c r="S61" t="n">
         <v>-0.08647309565511541</v>
       </c>
     </row>
@@ -3470,6 +3624,9 @@
         <v>0.1562357027461399</v>
       </c>
       <c r="R62" t="n">
+        <v>0.1558244391000705</v>
+      </c>
+      <c r="S62" t="n">
         <v>0.1558244391000704</v>
       </c>
     </row>
@@ -3528,6 +3685,9 @@
         <v>0.1525918190557647</v>
       </c>
       <c r="R63" t="n">
+        <v>0.1525325362021076</v>
+      </c>
+      <c r="S63" t="n">
         <v>0.1525325362021127</v>
       </c>
     </row>
@@ -3629,6 +3789,11 @@
           <t>FL</t>
         </is>
       </c>
+      <c r="S66" t="inlineStr">
+        <is>
+          <t>FedAvg</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -3685,6 +3850,9 @@
         <v>0.0297032591949156</v>
       </c>
       <c r="R67" t="n">
+        <v>0.0280888026830224</v>
+      </c>
+      <c r="S67" t="n">
         <v>0.035493275343358</v>
       </c>
     </row>
@@ -3743,6 +3911,9 @@
         <v>-0.1226686305064975</v>
       </c>
       <c r="R68" t="n">
+        <v>-0.1240622320617183</v>
+      </c>
+      <c r="S68" t="n">
         <v>-0.1166577594013838</v>
       </c>
     </row>
@@ -3801,6 +3972,9 @@
         <v>0.1708394505012818</v>
       </c>
       <c r="R69" t="n">
+        <v>0.1699020177137289</v>
+      </c>
+      <c r="S69" t="n">
         <v>0.1773064903740636</v>
       </c>
     </row>
@@ -3859,6 +4033,9 @@
         <v>0.1411361913063662</v>
       </c>
       <c r="R70" t="n">
+        <v>0.1418132150307065</v>
+      </c>
+      <c r="S70" t="n">
         <v>0.1418132150307056</v>
       </c>
     </row>
@@ -3917,6 +4094,9 @@
         <v>0.1523718897014131</v>
       </c>
       <c r="R71" t="n">
+        <v>0.1521510347447407</v>
+      </c>
+      <c r="S71" t="n">
         <v>0.1521510347447418</v>
       </c>
     </row>
@@ -4018,6 +4198,11 @@
           <t>FL</t>
         </is>
       </c>
+      <c r="S74" t="inlineStr">
+        <is>
+          <t>FedAvg</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -4074,6 +4259,9 @@
         <v>-0.1600473139784403</v>
       </c>
       <c r="R75" t="n">
+        <v>-0.1616324491936515</v>
+      </c>
+      <c r="S75" t="n">
         <v>-0.1632264747734452</v>
       </c>
     </row>
@@ -4132,6 +4320,9 @@
         <v>-0.4140460195076277</v>
       </c>
       <c r="R76" t="n">
+        <v>-0.4163736344730608</v>
+      </c>
+      <c r="S76" t="n">
         <v>-0.4179676600528515</v>
       </c>
     </row>
@@ -4190,6 +4381,9 @@
         <v>0.0493797935920237</v>
       </c>
       <c r="R77" t="n">
+        <v>0.047956498527165</v>
+      </c>
+      <c r="S77" t="n">
         <v>0.046362472947367</v>
       </c>
     </row>
@@ -4248,6 +4442,9 @@
         <v>0.209427107570464</v>
       </c>
       <c r="R78" t="n">
+        <v>0.2095889477208165</v>
+      </c>
+      <c r="S78" t="n">
         <v>0.2095889477208122</v>
       </c>
     </row>
@@ -4306,6 +4503,9 @@
         <v>0.2539987055291874</v>
       </c>
       <c r="R79" t="n">
+        <v>0.2547411852794093</v>
+      </c>
+      <c r="S79" t="n">
         <v>0.2547411852794063</v>
       </c>
     </row>
@@ -4407,6 +4607,11 @@
           <t>FL</t>
         </is>
       </c>
+      <c r="S82" t="inlineStr">
+        <is>
+          <t>FedAvg</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -4463,6 +4668,9 @@
         <v>0.0922245699360791</v>
       </c>
       <c r="R83" t="n">
+        <v>0.0929946219450505</v>
+      </c>
+      <c r="S83" t="n">
         <v>0.0993649363148216</v>
       </c>
     </row>
@@ -4521,6 +4729,9 @@
         <v>-0.0713161921702106</v>
       </c>
       <c r="R84" t="n">
+        <v>-0.0701773619804472</v>
+      </c>
+      <c r="S84" t="n">
         <v>-0.063807047610804</v>
       </c>
     </row>
@@ -4579,6 +4790,9 @@
         <v>0.2489923806540686</v>
       </c>
       <c r="R85" t="n">
+        <v>0.2506556660496545</v>
+      </c>
+      <c r="S85" t="n">
         <v>0.2570259804194256</v>
       </c>
     </row>
@@ -4639,6 +4853,9 @@
       <c r="R86" t="n">
         <v>0.157661044104604</v>
       </c>
+      <c r="S86" t="n">
+        <v>0.157661044104604</v>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -4695,6 +4912,9 @@
         <v>0.1635407621062897</v>
       </c>
       <c r="R87" t="n">
+        <v>0.1631719839254977</v>
+      </c>
+      <c r="S87" t="n">
         <v>0.1631719839256256</v>
       </c>
     </row>
@@ -4796,6 +5016,11 @@
           <t>FL</t>
         </is>
       </c>
+      <c r="S90" t="inlineStr">
+        <is>
+          <t>FedAvg</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -4852,6 +5077,9 @@
         <v>-0.1566185324519521</v>
       </c>
       <c r="R91" t="n">
+        <v>-0.1547776401316559</v>
+      </c>
+      <c r="S91" t="n">
         <v>-0.1498051503442583</v>
       </c>
     </row>
@@ -4910,6 +5138,9 @@
         <v>-0.2886108884033905</v>
       </c>
       <c r="R92" t="n">
+        <v>-0.2860834412752014</v>
+      </c>
+      <c r="S92" t="n">
         <v>-0.2811109514878037</v>
       </c>
     </row>
@@ -4968,6 +5199,9 @@
         <v>-0.0337670809814191</v>
       </c>
       <c r="R93" t="n">
+        <v>-0.0327517058014342</v>
+      </c>
+      <c r="S93" t="n">
         <v>-0.0277792160140367</v>
       </c>
     </row>
@@ -5026,6 +5260,9 @@
         <v>0.122851451470533</v>
       </c>
       <c r="R94" t="n">
+        <v>0.1220259343302217</v>
+      </c>
+      <c r="S94" t="n">
         <v>0.1220259343302216</v>
       </c>
     </row>
@@ -5084,6 +5321,9 @@
         <v>0.1319923559514384</v>
       </c>
       <c r="R95" t="n">
+        <v>0.1313058011435455</v>
+      </c>
+      <c r="S95" t="n">
         <v>0.1313058011435454</v>
       </c>
     </row>
@@ -5185,6 +5425,11 @@
           <t>FL</t>
         </is>
       </c>
+      <c r="S98" t="inlineStr">
+        <is>
+          <t>FedAvg</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -5241,6 +5486,9 @@
         <v>-0.2478361778535859</v>
       </c>
       <c r="R99" t="n">
+        <v>-0.2471309190996203</v>
+      </c>
+      <c r="S99" t="n">
         <v>-0.2481800450383744</v>
       </c>
     </row>
@@ -5299,6 +5547,9 @@
         <v>-0.4533825194907221</v>
       </c>
       <c r="R100" t="n">
+        <v>-0.4532611573747188</v>
+      </c>
+      <c r="S100" t="n">
         <v>-0.454310283313473</v>
       </c>
     </row>
@@ -5357,6 +5608,9 @@
         <v>-0.0738333327615652</v>
       </c>
       <c r="R101" t="n">
+        <v>-0.0724959590356109</v>
+      </c>
+      <c r="S101" t="n">
         <v>-0.0735450849743652</v>
       </c>
     </row>
@@ -5415,6 +5669,9 @@
         <v>0.1740028450920207</v>
       </c>
       <c r="R102" t="n">
+        <v>0.1746349600640094</v>
+      </c>
+      <c r="S102" t="n">
         <v>0.1746349600640092</v>
       </c>
     </row>
@@ -5473,6 +5730,9 @@
         <v>0.2055463416371362</v>
       </c>
       <c r="R103" t="n">
+        <v>0.2061302382750985</v>
+      </c>
+      <c r="S103" t="n">
         <v>0.2061302382750986</v>
       </c>
     </row>
@@ -5574,6 +5834,11 @@
           <t>FL</t>
         </is>
       </c>
+      <c r="S106" t="inlineStr">
+        <is>
+          <t>FedAvg</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -5630,6 +5895,9 @@
         <v>0.1270466837348472</v>
       </c>
       <c r="R107" t="n">
+        <v>0.127465163725077</v>
+      </c>
+      <c r="S107" t="n">
         <v>0.1346564868491306</v>
       </c>
     </row>
@@ -5688,6 +5956,9 @@
         <v>-0.0137546090444073</v>
       </c>
       <c r="R108" t="n">
+        <v>-0.0130548746438242</v>
+      </c>
+      <c r="S108" t="n">
         <v>-0.0058635515197708</v>
       </c>
     </row>
@@ -5746,6 +6017,9 @@
         <v>0.2595075062574232</v>
       </c>
       <c r="R109" t="n">
+        <v>0.2595909761086788</v>
+      </c>
+      <c r="S109" t="n">
         <v>0.2667822992327322</v>
       </c>
     </row>
@@ -5804,6 +6078,9 @@
         <v>0.132460822522576</v>
       </c>
       <c r="R110" t="n">
+        <v>0.1321258123836018</v>
+      </c>
+      <c r="S110" t="n">
         <v>0.1321258123836016</v>
       </c>
     </row>
@@ -5862,6 +6139,9 @@
         <v>0.1408012927792545</v>
       </c>
       <c r="R111" t="n">
+        <v>0.1405200383689012</v>
+      </c>
+      <c r="S111" t="n">
         <v>0.1405200383689014</v>
       </c>
     </row>
@@ -5963,6 +6243,11 @@
           <t>FL</t>
         </is>
       </c>
+      <c r="S114" t="inlineStr">
+        <is>
+          <t>FedAvg</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -6019,6 +6304,9 @@
         <v>-0.07921902201735929</v>
       </c>
       <c r="R115" t="n">
+        <v>-0.08074975351795879</v>
+      </c>
+      <c r="S115" t="n">
         <v>-0.0786137214269897</v>
       </c>
     </row>
@@ -6077,6 +6365,9 @@
         <v>-0.2536486888496191</v>
       </c>
       <c r="R116" t="n">
+        <v>-0.2543735749041315</v>
+      </c>
+      <c r="S116" t="n">
         <v>-0.2522375428131623</v>
       </c>
     </row>
@@ -6135,6 +6426,9 @@
         <v>0.08410158359322541</v>
       </c>
       <c r="R117" t="n">
+        <v>0.0824786926490701</v>
+      </c>
+      <c r="S117" t="n">
         <v>0.0846147247400392</v>
       </c>
     </row>
@@ -6195,6 +6489,9 @@
       <c r="R118" t="n">
         <v>0.1632284461670289</v>
       </c>
+      <c r="S118" t="n">
+        <v>0.1632284461670289</v>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -6251,6 +6548,9 @@
         <v>0.1744296668322598</v>
       </c>
       <c r="R119" t="n">
+        <v>0.1736238213861727</v>
+      </c>
+      <c r="S119" t="n">
         <v>0.1736238213861726</v>
       </c>
     </row>
@@ -6352,6 +6652,11 @@
           <t>FL</t>
         </is>
       </c>
+      <c r="S122" t="inlineStr">
+        <is>
+          <t>FedAvg</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -6408,6 +6713,9 @@
         <v>0.2773480154348374</v>
       </c>
       <c r="R123" t="n">
+        <v>0.2631202358313751</v>
+      </c>
+      <c r="S123" t="n">
         <v>0.2646278273325543</v>
       </c>
     </row>
@@ -6466,6 +6774,9 @@
         <v>0.046066757849865</v>
       </c>
       <c r="R124" t="n">
+        <v>0.0333400092227222</v>
+      </c>
+      <c r="S124" t="n">
         <v>0.0348476007239019</v>
       </c>
     </row>
@@ -6524,6 +6835,9 @@
         <v>0.4862736753278965</v>
       </c>
       <c r="R125" t="n">
+        <v>0.4715812148900709</v>
+      </c>
+      <c r="S125" t="n">
         <v>0.4730888063912501</v>
       </c>
     </row>
@@ -6584,6 +6898,9 @@
       <c r="R126" t="n">
         <v>0.2084609790586958</v>
       </c>
+      <c r="S126" t="n">
+        <v>0.2084609790586958</v>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -6640,6 +6957,9 @@
         <v>0.2312812575849724</v>
       </c>
       <c r="R127" t="n">
+        <v>0.2297802266086529</v>
+      </c>
+      <c r="S127" t="n">
         <v>0.2297802266086524</v>
       </c>
     </row>
@@ -6654,7 +6974,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R127"/>
+  <dimension ref="A1:S127"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6755,6 +7075,11 @@
           <t>FL</t>
         </is>
       </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>FedAvg</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -6811,6 +7136,9 @@
         <v>0.0074767964764659</v>
       </c>
       <c r="R3" t="n">
+        <v>0.0131472267622466</v>
+      </c>
+      <c r="S3" t="n">
         <v>0.1302009816144933</v>
       </c>
     </row>
@@ -6869,6 +7197,9 @@
         <v>-0.1805862471852536</v>
       </c>
       <c r="R4" t="n">
+        <v>-0.1757556725341595</v>
+      </c>
+      <c r="S4" t="n">
         <v>-0.0587019176818141</v>
       </c>
     </row>
@@ -6927,6 +7258,9 @@
         <v>0.175918382691308</v>
       </c>
       <c r="R5" t="n">
+        <v>0.1847442786697766</v>
+      </c>
+      <c r="S5" t="n">
         <v>0.3017980335220242</v>
       </c>
     </row>
@@ -6985,6 +7319,9 @@
         <v>0.1684415862148421</v>
       </c>
       <c r="R6" t="n">
+        <v>0.17159705190753</v>
+      </c>
+      <c r="S6" t="n">
         <v>0.1715970519075309</v>
       </c>
     </row>
@@ -7043,6 +7380,9 @@
         <v>0.1880630436617195</v>
       </c>
       <c r="R7" t="n">
+        <v>0.1889028992964061</v>
+      </c>
+      <c r="S7" t="n">
         <v>0.1889028992963074</v>
       </c>
     </row>
@@ -7144,6 +7484,11 @@
           <t>FL</t>
         </is>
       </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>FedAvg</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -7200,6 +7545,9 @@
         <v>0.073884721786922</v>
       </c>
       <c r="R11" t="n">
+        <v>0.06740696222105109</v>
+      </c>
+      <c r="S11" t="n">
         <v>0.2025839089260948</v>
       </c>
     </row>
@@ -7258,6 +7606,9 @@
         <v>-0.07703561601763941</v>
       </c>
       <c r="R12" t="n">
+        <v>-0.08534126437999939</v>
+      </c>
+      <c r="S12" t="n">
         <v>0.0498356823252399</v>
       </c>
     </row>
@@ -7316,6 +7667,9 @@
         <v>0.2084035584612507</v>
       </c>
       <c r="R13" t="n">
+        <v>0.2037276251327321</v>
+      </c>
+      <c r="S13" t="n">
         <v>0.3389045718379541</v>
       </c>
     </row>
@@ -7374,6 +7728,9 @@
         <v>0.1345188366743287</v>
       </c>
       <c r="R14" t="n">
+        <v>0.136320662911681</v>
+      </c>
+      <c r="S14" t="n">
         <v>0.1363206629118593</v>
       </c>
     </row>
@@ -7432,6 +7789,9 @@
         <v>0.1509203378045614</v>
       </c>
       <c r="R15" t="n">
+        <v>0.1527482266010505</v>
+      </c>
+      <c r="S15" t="n">
         <v>0.1527482266008549</v>
       </c>
     </row>
@@ -7533,6 +7893,11 @@
           <t>FL</t>
         </is>
       </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>FedAvg</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -7589,6 +7954,9 @@
         <v>-0.0012842372030356</v>
       </c>
       <c r="R19" t="n">
+        <v>-0.0218374223543954</v>
+      </c>
+      <c r="S19" t="n">
         <v>0.08645405982010861</v>
       </c>
     </row>
@@ -7647,6 +8015,9 @@
         <v>-0.1812594312086517</v>
       </c>
       <c r="R20" t="n">
+        <v>-0.2059888768380099</v>
+      </c>
+      <c r="S20" t="n">
         <v>-0.0976973946635057</v>
       </c>
     </row>
@@ -7705,6 +8076,9 @@
         <v>0.1716710362163565</v>
       </c>
       <c r="R21" t="n">
+        <v>0.1553041330693406</v>
+      </c>
+      <c r="S21" t="n">
         <v>0.263595615243845</v>
       </c>
     </row>
@@ -7763,6 +8137,9 @@
         <v>0.1729552734193921</v>
       </c>
       <c r="R22" t="n">
+        <v>0.177141555423736</v>
+      </c>
+      <c r="S22" t="n">
         <v>0.1771415554237364</v>
       </c>
     </row>
@@ -7821,6 +8198,9 @@
         <v>0.1799751940056161</v>
       </c>
       <c r="R23" t="n">
+        <v>0.1841514544836145</v>
+      </c>
+      <c r="S23" t="n">
         <v>0.1841514544836143</v>
       </c>
     </row>
@@ -7922,6 +8302,11 @@
           <t>FL</t>
         </is>
       </c>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>FedAvg</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -7978,6 +8363,9 @@
         <v>0.1462486842187141</v>
       </c>
       <c r="R27" t="n">
+        <v>0.1573871787092243</v>
+      </c>
+      <c r="S27" t="n">
         <v>0.3205494715495294</v>
       </c>
     </row>
@@ -8036,6 +8424,9 @@
         <v>-0.0079209776917893</v>
       </c>
       <c r="R28" t="n">
+        <v>0.0023960872451292</v>
+      </c>
+      <c r="S28" t="n">
         <v>0.165558380085432</v>
       </c>
     </row>
@@ -8094,6 +8485,9 @@
         <v>0.2814853454265329</v>
       </c>
       <c r="R29" t="n">
+        <v>0.2926895678121607</v>
+      </c>
+      <c r="S29" t="n">
         <v>0.4558518606524634</v>
       </c>
     </row>
@@ -8152,6 +8546,9 @@
         <v>0.1352366612078188</v>
       </c>
       <c r="R30" t="n">
+        <v>0.1353023891029364</v>
+      </c>
+      <c r="S30" t="n">
         <v>0.135302389102934</v>
       </c>
     </row>
@@ -8210,6 +8607,9 @@
         <v>0.1541696619105034</v>
       </c>
       <c r="R31" t="n">
+        <v>0.1549910914640951</v>
+      </c>
+      <c r="S31" t="n">
         <v>0.1549910914640974</v>
       </c>
     </row>
@@ -8311,6 +8711,11 @@
           <t>FL</t>
         </is>
       </c>
+      <c r="S34" t="inlineStr">
+        <is>
+          <t>FedAvg</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -8367,6 +8772,9 @@
         <v>0.08855888289285339</v>
       </c>
       <c r="R35" t="n">
+        <v>0.1189329571831926</v>
+      </c>
+      <c r="S35" t="n">
         <v>0.2375752355825344</v>
       </c>
     </row>
@@ -8425,6 +8833,9 @@
         <v>-0.1221625535165224</v>
       </c>
       <c r="R36" t="n">
+        <v>-0.09763541953762481</v>
+      </c>
+      <c r="S36" t="n">
         <v>0.021006858861717</v>
       </c>
     </row>
@@ -8483,6 +8894,9 @@
         <v>0.2676610120884365</v>
       </c>
       <c r="R37" t="n">
+        <v>0.2994477700511285</v>
+      </c>
+      <c r="S37" t="n">
         <v>0.4180900484505929</v>
       </c>
     </row>
@@ -8541,6 +8955,9 @@
         <v>0.1791021291955831</v>
       </c>
       <c r="R38" t="n">
+        <v>0.1805148128679359</v>
+      </c>
+      <c r="S38" t="n">
         <v>0.1805148128680585</v>
       </c>
     </row>
@@ -8601,6 +9018,9 @@
       <c r="R39" t="n">
         <v>0.2165683767208174</v>
       </c>
+      <c r="S39" t="n">
+        <v>0.2165683767208174</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -8700,6 +9120,11 @@
           <t>FL</t>
         </is>
       </c>
+      <c r="S42" t="inlineStr">
+        <is>
+          <t>FedAvg</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -8756,6 +9181,9 @@
         <v>0.1949024154403741</v>
       </c>
       <c r="R43" t="n">
+        <v>0.1892557753269309</v>
+      </c>
+      <c r="S43" t="n">
         <v>0.2730475495267887</v>
       </c>
     </row>
@@ -8814,6 +9242,9 @@
         <v>-0.0267737180855807</v>
       </c>
       <c r="R44" t="n">
+        <v>-0.0369857053118267</v>
+      </c>
+      <c r="S44" t="n">
         <v>0.0468060688880371</v>
       </c>
     </row>
@@ -8872,6 +9303,9 @@
         <v>0.3924793419656882</v>
       </c>
       <c r="R45" t="n">
+        <v>0.393601998478747</v>
+      </c>
+      <c r="S45" t="n">
         <v>0.477393772678831</v>
       </c>
     </row>
@@ -8930,6 +9364,9 @@
         <v>0.1975769265253141</v>
       </c>
       <c r="R46" t="n">
+        <v>0.2043462231518161</v>
+      </c>
+      <c r="S46" t="n">
         <v>0.2043462231520423</v>
       </c>
     </row>
@@ -8988,6 +9425,9 @@
         <v>0.2216761335259548</v>
       </c>
       <c r="R47" t="n">
+        <v>0.2262414806387576</v>
+      </c>
+      <c r="S47" t="n">
         <v>0.2262414806387516</v>
       </c>
     </row>
@@ -9089,6 +9529,11 @@
           <t>FL</t>
         </is>
       </c>
+      <c r="S50" t="inlineStr">
+        <is>
+          <t>FedAvg</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -9145,6 +9590,9 @@
         <v>0.0118644073919565</v>
       </c>
       <c r="R51" t="n">
+        <v>0.0145385935541693</v>
+      </c>
+      <c r="S51" t="n">
         <v>0.2176919930048476</v>
       </c>
     </row>
@@ -9203,6 +9651,9 @@
         <v>-0.1597968576387408</v>
       </c>
       <c r="R52" t="n">
+        <v>-0.1571640313625778</v>
+      </c>
+      <c r="S52" t="n">
         <v>0.0459893680881133</v>
       </c>
     </row>
@@ -9261,6 +9712,9 @@
         <v>0.1549864361834096</v>
       </c>
       <c r="R53" t="n">
+        <v>0.159198542694962</v>
+      </c>
+      <c r="S53" t="n">
         <v>0.3623519421456528</v>
       </c>
     </row>
@@ -9319,6 +9773,9 @@
         <v>0.1431220287914531</v>
       </c>
       <c r="R54" t="n">
+        <v>0.1446599491407927</v>
+      </c>
+      <c r="S54" t="n">
         <v>0.1446599491408052</v>
       </c>
     </row>
@@ -9377,6 +9834,9 @@
         <v>0.1716612650306973</v>
       </c>
       <c r="R55" t="n">
+        <v>0.1717026249167471</v>
+      </c>
+      <c r="S55" t="n">
         <v>0.1717026249167343</v>
       </c>
     </row>
@@ -9478,6 +9938,11 @@
           <t>FL</t>
         </is>
       </c>
+      <c r="S58" t="inlineStr">
+        <is>
+          <t>FedAvg</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -9534,6 +9999,9 @@
         <v>-0.2545572114076269</v>
       </c>
       <c r="R59" t="n">
+        <v>-0.2622419552851344</v>
+      </c>
+      <c r="S59" t="n">
         <v>-0.1162955089081267</v>
       </c>
     </row>
@@ -9592,6 +10060,9 @@
         <v>-0.4070442707590656</v>
       </c>
       <c r="R60" t="n">
+        <v>-0.4160345450433269</v>
+      </c>
+      <c r="S60" t="n">
         <v>-0.2700880986663436</v>
       </c>
     </row>
@@ -9650,6 +10121,9 @@
         <v>-0.0984411523336583</v>
       </c>
       <c r="R61" t="n">
+        <v>-0.1057177695866871</v>
+      </c>
+      <c r="S61" t="n">
         <v>0.0402286767903241</v>
       </c>
     </row>
@@ -9708,6 +10182,9 @@
         <v>0.1561160590739686</v>
       </c>
       <c r="R62" t="n">
+        <v>0.1565241856984473</v>
+      </c>
+      <c r="S62" t="n">
         <v>0.1565241856984508</v>
       </c>
     </row>
@@ -9766,6 +10243,9 @@
         <v>0.1524870593514387</v>
       </c>
       <c r="R63" t="n">
+        <v>0.1537925897581925</v>
+      </c>
+      <c r="S63" t="n">
         <v>0.1537925897582169</v>
       </c>
     </row>
@@ -9867,6 +10347,11 @@
           <t>FL</t>
         </is>
       </c>
+      <c r="S66" t="inlineStr">
+        <is>
+          <t>FedAvg</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -9923,6 +10408,9 @@
         <v>0.0292186709613114</v>
       </c>
       <c r="R67" t="n">
+        <v>0.028348719087706</v>
+      </c>
+      <c r="S67" t="n">
         <v>0.1637273151937678</v>
       </c>
     </row>
@@ -9981,6 +10469,9 @@
         <v>-0.1231286710010398</v>
       </c>
       <c r="R68" t="n">
+        <v>-0.1275353956222103</v>
+      </c>
+      <c r="S68" t="n">
         <v>0.007843200483851599</v>
       </c>
     </row>
@@ -10039,6 +10530,9 @@
         <v>0.1703376106268161</v>
       </c>
       <c r="R69" t="n">
+        <v>0.174127965757281</v>
+      </c>
+      <c r="S69" t="n">
         <v>0.3095065618633438</v>
       </c>
     </row>
@@ -10097,6 +10591,9 @@
         <v>0.1411189396655047</v>
       </c>
       <c r="R70" t="n">
+        <v>0.145779246669575</v>
+      </c>
+      <c r="S70" t="n">
         <v>0.145779246669576</v>
       </c>
     </row>
@@ -10155,6 +10652,9 @@
         <v>0.1523473419623512</v>
       </c>
       <c r="R71" t="n">
+        <v>0.1558841147099163</v>
+      </c>
+      <c r="S71" t="n">
         <v>0.1558841147099162</v>
       </c>
     </row>
@@ -10256,6 +10756,11 @@
           <t>FL</t>
         </is>
       </c>
+      <c r="S74" t="inlineStr">
+        <is>
+          <t>FedAvg</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -10312,6 +10817,9 @@
         <v>-0.1605847307836596</v>
       </c>
       <c r="R75" t="n">
+        <v>-0.1685171491207751</v>
+      </c>
+      <c r="S75" t="n">
         <v>-0.0732532927575537</v>
       </c>
     </row>
@@ -10370,6 +10878,9 @@
         <v>-0.4145498687354775</v>
       </c>
       <c r="R76" t="n">
+        <v>-0.4322888074892647</v>
+      </c>
+      <c r="S76" t="n">
         <v>-0.3370249511261047</v>
       </c>
     </row>
@@ -10428,6 +10939,9 @@
         <v>0.0488635052492576</v>
       </c>
       <c r="R77" t="n">
+        <v>0.0456582442021197</v>
+      </c>
+      <c r="S77" t="n">
         <v>0.140922100565331</v>
       </c>
     </row>
@@ -10486,6 +11000,9 @@
         <v>0.2094482360329172</v>
       </c>
       <c r="R78" t="n">
+        <v>0.2141753933228948</v>
+      </c>
+      <c r="S78" t="n">
         <v>0.2141753933228847</v>
       </c>
     </row>
@@ -10544,6 +11061,9 @@
         <v>0.2539651379518179</v>
       </c>
       <c r="R79" t="n">
+        <v>0.2637716583684896</v>
+      </c>
+      <c r="S79" t="n">
         <v>0.263771658368551</v>
       </c>
     </row>
@@ -10645,6 +11165,11 @@
           <t>FL</t>
         </is>
       </c>
+      <c r="S82" t="inlineStr">
+        <is>
+          <t>FedAvg</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -10701,6 +11226,9 @@
         <v>0.0923074803214509</v>
       </c>
       <c r="R83" t="n">
+        <v>0.09110582634481861</v>
+      </c>
+      <c r="S83" t="n">
         <v>0.1678395758296506</v>
       </c>
     </row>
@@ -10759,6 +11287,9 @@
         <v>-0.07122103051540039</v>
       </c>
       <c r="R84" t="n">
+        <v>-0.0749510046547576</v>
+      </c>
+      <c r="S84" t="n">
         <v>0.0017827448300751</v>
       </c>
     </row>
@@ -10817,6 +11348,9 @@
         <v>0.2489042986847356</v>
       </c>
       <c r="R85" t="n">
+        <v>0.2539930315828432</v>
+      </c>
+      <c r="S85" t="n">
         <v>0.3307267810676764</v>
       </c>
     </row>
@@ -10875,6 +11409,9 @@
         <v>0.1565968183632847</v>
       </c>
       <c r="R86" t="n">
+        <v>0.1628872052380246</v>
+      </c>
+      <c r="S86" t="n">
         <v>0.1628872052380258</v>
       </c>
     </row>
@@ -10933,6 +11470,9 @@
         <v>0.1635285108368513</v>
       </c>
       <c r="R87" t="n">
+        <v>0.1660568309995762</v>
+      </c>
+      <c r="S87" t="n">
         <v>0.1660568309995755</v>
       </c>
     </row>
@@ -11034,6 +11574,11 @@
           <t>FL</t>
         </is>
       </c>
+      <c r="S90" t="inlineStr">
+        <is>
+          <t>FedAvg</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -11090,6 +11635,9 @@
         <v>-0.156842730160337</v>
       </c>
       <c r="R91" t="n">
+        <v>-0.1507618530373703</v>
+      </c>
+      <c r="S91" t="n">
         <v>0.0684192007290578</v>
       </c>
     </row>
@@ -11148,6 +11696,9 @@
         <v>-0.2888037331678492</v>
       </c>
       <c r="R92" t="n">
+        <v>-0.2855170448851195</v>
+      </c>
+      <c r="S92" t="n">
         <v>-0.066335991118745</v>
       </c>
     </row>
@@ -11206,6 +11757,9 @@
         <v>-0.0340309693521669</v>
       </c>
       <c r="R93" t="n">
+        <v>-0.0285950660869238</v>
+      </c>
+      <c r="S93" t="n">
         <v>0.1905859876792464</v>
       </c>
     </row>
@@ -11264,6 +11818,9 @@
         <v>0.1228117608081701</v>
       </c>
       <c r="R94" t="n">
+        <v>0.1221667869504465</v>
+      </c>
+      <c r="S94" t="n">
         <v>0.1221667869501886</v>
       </c>
     </row>
@@ -11322,6 +11879,9 @@
         <v>0.1319610030075122</v>
       </c>
       <c r="R95" t="n">
+        <v>0.1347551918477492</v>
+      </c>
+      <c r="S95" t="n">
         <v>0.1347551918478028</v>
       </c>
     </row>
@@ -11423,6 +11983,11 @@
           <t>FL</t>
         </is>
       </c>
+      <c r="S98" t="inlineStr">
+        <is>
+          <t>FedAvg</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -11479,6 +12044,9 @@
         <v>-0.2478480008109096</v>
       </c>
       <c r="R99" t="n">
+        <v>-0.2430383745017312</v>
+      </c>
+      <c r="S99" t="n">
         <v>-0.0881964996781474</v>
       </c>
     </row>
@@ -11537,6 +12105,9 @@
         <v>-0.4533625073603154</v>
       </c>
       <c r="R100" t="n">
+        <v>-0.4511255307804594</v>
+      </c>
+      <c r="S100" t="n">
         <v>-0.2962836559568831</v>
       </c>
     </row>
@@ -11595,6 +12166,9 @@
         <v>-0.073912157473385</v>
       </c>
       <c r="R101" t="n">
+        <v>-0.0669549938812584</v>
+      </c>
+      <c r="S101" t="n">
         <v>0.08788688094208109</v>
       </c>
     </row>
@@ -11653,6 +12227,9 @@
         <v>0.1739358433375246</v>
       </c>
       <c r="R102" t="n">
+        <v>0.1760833806204728</v>
+      </c>
+      <c r="S102" t="n">
         <v>0.1760833806202285</v>
       </c>
     </row>
@@ -11711,6 +12288,9 @@
         <v>0.2055145065494058</v>
       </c>
       <c r="R103" t="n">
+        <v>0.2080871562787282</v>
+      </c>
+      <c r="S103" t="n">
         <v>0.2080871562787357</v>
       </c>
     </row>
@@ -11812,6 +12392,11 @@
           <t>FL</t>
         </is>
       </c>
+      <c r="S106" t="inlineStr">
+        <is>
+          <t>FedAvg</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -11868,6 +12453,9 @@
         <v>0.1267842579991214</v>
       </c>
       <c r="R107" t="n">
+        <v>0.1186857214474277</v>
+      </c>
+      <c r="S107" t="n">
         <v>0.2871093030786806</v>
       </c>
     </row>
@@ -11926,6 +12514,9 @@
         <v>-0.01419172473683</v>
       </c>
       <c r="R108" t="n">
+        <v>-0.0229365198074838</v>
+      </c>
+      <c r="S108" t="n">
         <v>0.1454870618237686</v>
       </c>
     </row>
@@ -11984,6 +12575,9 @@
         <v>0.2591706313784124</v>
       </c>
       <c r="R109" t="n">
+        <v>0.2528228705569174</v>
+      </c>
+      <c r="S109" t="n">
         <v>0.4212464521882639</v>
       </c>
     </row>
@@ -12042,6 +12636,9 @@
         <v>0.132386373379291</v>
       </c>
       <c r="R110" t="n">
+        <v>0.1341371491094897</v>
+      </c>
+      <c r="S110" t="n">
         <v>0.1341371491095833</v>
       </c>
     </row>
@@ -12100,6 +12697,9 @@
         <v>0.1409759827359514</v>
       </c>
       <c r="R111" t="n">
+        <v>0.1416222412549115</v>
+      </c>
+      <c r="S111" t="n">
         <v>0.141622241254912</v>
       </c>
     </row>
@@ -12201,6 +12801,11 @@
           <t>FL</t>
         </is>
       </c>
+      <c r="S114" t="inlineStr">
+        <is>
+          <t>FedAvg</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -12257,6 +12862,9 @@
         <v>-0.0795046874574656</v>
       </c>
       <c r="R115" t="n">
+        <v>-0.06492813518150981</v>
+      </c>
+      <c r="S115" t="n">
         <v>0.0280318699739308</v>
       </c>
     </row>
@@ -12315,6 +12923,9 @@
         <v>-0.2539597613856128</v>
       </c>
       <c r="R116" t="n">
+        <v>-0.2444113473072446</v>
+      </c>
+      <c r="S116" t="n">
         <v>-0.1514513421516147</v>
       </c>
     </row>
@@ -12373,6 +12984,9 @@
         <v>0.0837586860604902</v>
       </c>
       <c r="R117" t="n">
+        <v>0.1020176529923611</v>
+      </c>
+      <c r="S117" t="n">
         <v>0.1949776581479911</v>
       </c>
     </row>
@@ -12431,6 +13045,9 @@
         <v>0.1632633735179558</v>
       </c>
       <c r="R118" t="n">
+        <v>0.1669457881738709</v>
+      </c>
+      <c r="S118" t="n">
         <v>0.1669457881740603</v>
       </c>
     </row>
@@ -12489,6 +13106,9 @@
         <v>0.1744550739281472</v>
       </c>
       <c r="R119" t="n">
+        <v>0.1794832121257348</v>
+      </c>
+      <c r="S119" t="n">
         <v>0.1794832121255455</v>
       </c>
     </row>
@@ -12590,6 +13210,11 @@
           <t>FL</t>
         </is>
       </c>
+      <c r="S122" t="inlineStr">
+        <is>
+          <t>FedAvg</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -12646,6 +13271,9 @@
         <v>0.2764146820721832</v>
       </c>
       <c r="R123" t="n">
+        <v>0.2766031733083</v>
+      </c>
+      <c r="S123" t="n">
         <v>0.4104329680027981</v>
       </c>
     </row>
@@ -12704,6 +13332,9 @@
         <v>0.0451861838805371</v>
       </c>
       <c r="R124" t="n">
+        <v>0.0442508991706071</v>
+      </c>
+      <c r="S124" t="n">
         <v>0.1780806938648924</v>
       </c>
     </row>
@@ -12762,6 +13393,9 @@
         <v>0.4853461628723039</v>
       </c>
       <c r="R125" t="n">
+        <v>0.4861914000617041</v>
+      </c>
+      <c r="S125" t="n">
         <v>0.6200211947559988</v>
       </c>
     </row>
@@ -12820,6 +13454,9 @@
         <v>0.2089314808001207</v>
       </c>
       <c r="R126" t="n">
+        <v>0.2095882267534041</v>
+      </c>
+      <c r="S126" t="n">
         <v>0.2095882267532007</v>
       </c>
     </row>
@@ -12878,6 +13515,9 @@
         <v>0.2312284981916461</v>
       </c>
       <c r="R127" t="n">
+        <v>0.2323522741376929</v>
+      </c>
+      <c r="S127" t="n">
         <v>0.2323522741379057</v>
       </c>
     </row>
@@ -12892,7 +13532,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R127"/>
+  <dimension ref="A1:S127"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12993,6 +13633,11 @@
           <t>FL</t>
         </is>
       </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>FedAvg</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -13049,6 +13694,9 @@
         <v>0.0080545461390602</v>
       </c>
       <c r="R3" t="n">
+        <v>0.0045181077604228</v>
+      </c>
+      <c r="S3" t="n">
         <v>0.0142852758376569</v>
       </c>
     </row>
@@ -13107,6 +13755,9 @@
         <v>-0.1799521606229232</v>
       </c>
       <c r="R4" t="n">
+        <v>-0.1844077545178273</v>
+      </c>
+      <c r="S4" t="n">
         <v>-0.1746405864405934</v>
       </c>
     </row>
@@ -13165,6 +13816,9 @@
         <v>0.1765126615488735</v>
       </c>
       <c r="R5" t="n">
+        <v>0.1726843755511211</v>
+      </c>
+      <c r="S5" t="n">
         <v>0.1824515436283552</v>
       </c>
     </row>
@@ -13225,6 +13879,9 @@
       <c r="R6" t="n">
         <v>0.1681662677906983</v>
       </c>
+      <c r="S6" t="n">
+        <v>0.1681662677906983</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -13281,6 +13938,9 @@
         <v>0.1880067067619834</v>
       </c>
       <c r="R7" t="n">
+        <v>0.1889258622782501</v>
+      </c>
+      <c r="S7" t="n">
         <v>0.1889258622782503</v>
       </c>
     </row>
@@ -13382,6 +14042,11 @@
           <t>FL</t>
         </is>
       </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>FedAvg</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -13438,6 +14103,9 @@
         <v>0.0738739982303311</v>
       </c>
       <c r="R11" t="n">
+        <v>0.0710289398276185</v>
+      </c>
+      <c r="S11" t="n">
         <v>0.0782908548273199</v>
       </c>
     </row>
@@ -13496,6 +14164,9 @@
         <v>-0.07713013980197719</v>
       </c>
       <c r="R12" t="n">
+        <v>-0.0800034406653459</v>
+      </c>
+      <c r="S12" t="n">
         <v>-0.0727415256653445</v>
       </c>
     </row>
@@ -13554,6 +14225,9 @@
         <v>0.2083112935790958</v>
       </c>
       <c r="R13" t="n">
+        <v>0.2050309692504</v>
+      </c>
+      <c r="S13" t="n">
         <v>0.2122928842504012</v>
       </c>
     </row>
@@ -13612,6 +14286,9 @@
         <v>0.1344372953487647</v>
       </c>
       <c r="R14" t="n">
+        <v>0.1340020294227815</v>
+      </c>
+      <c r="S14" t="n">
         <v>0.1340020294230813</v>
       </c>
     </row>
@@ -13670,6 +14347,9 @@
         <v>0.1510041380323083</v>
       </c>
       <c r="R15" t="n">
+        <v>0.1510323804929644</v>
+      </c>
+      <c r="S15" t="n">
         <v>0.1510323804926644</v>
       </c>
     </row>
@@ -13771,6 +14451,11 @@
           <t>FL</t>
         </is>
       </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>FedAvg</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -13827,6 +14512,9 @@
         <v>-0.0006719783745961</v>
       </c>
       <c r="R19" t="n">
+        <v>-0.000495493653757</v>
+      </c>
+      <c r="S19" t="n">
         <v>0.0042151466157354</v>
       </c>
     </row>
@@ -13885,6 +14573,9 @@
         <v>-0.1806073320121253</v>
       </c>
       <c r="R20" t="n">
+        <v>-0.1810659818926794</v>
+      </c>
+      <c r="S20" t="n">
         <v>-0.1763553416231848</v>
       </c>
     </row>
@@ -13943,6 +14634,9 @@
         <v>0.1722448775294019</v>
       </c>
       <c r="R21" t="n">
+        <v>0.1724061539613062</v>
+      </c>
+      <c r="S21" t="n">
         <v>0.1771167942308008</v>
       </c>
     </row>
@@ -14001,6 +14695,9 @@
         <v>0.172916855903998</v>
       </c>
       <c r="R22" t="n">
+        <v>0.1729016476150632</v>
+      </c>
+      <c r="S22" t="n">
         <v>0.1729016476150654</v>
       </c>
     </row>
@@ -14059,6 +14756,9 @@
         <v>0.1799353536375292</v>
       </c>
       <c r="R23" t="n">
+        <v>0.1805704882389224</v>
+      </c>
+      <c r="S23" t="n">
         <v>0.1805704882389202</v>
       </c>
     </row>
@@ -14160,6 +14860,11 @@
           <t>FL</t>
         </is>
       </c>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>FedAvg</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -14216,6 +14921,9 @@
         <v>0.1468550114706514</v>
       </c>
       <c r="R27" t="n">
+        <v>0.1447682926577187</v>
+      </c>
+      <c r="S27" t="n">
         <v>0.1519682239104185</v>
       </c>
     </row>
@@ -14274,6 +14982,9 @@
         <v>-0.0073343906509548</v>
       </c>
       <c r="R28" t="n">
+        <v>-0.0093455524176885</v>
+      </c>
+      <c r="S28" t="n">
         <v>-0.0021456211649888</v>
       </c>
     </row>
@@ -14332,6 +15043,9 @@
         <v>0.282180229738965</v>
       </c>
       <c r="R29" t="n">
+        <v>0.2794431464281774</v>
+      </c>
+      <c r="S29" t="n">
         <v>0.2866430776808772</v>
       </c>
     </row>
@@ -14392,6 +15106,9 @@
       <c r="R30" t="n">
         <v>0.1346748537704587</v>
       </c>
+      <c r="S30" t="n">
+        <v>0.1346748537704587</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -14448,6 +15165,9 @@
         <v>0.1541894021216062</v>
       </c>
       <c r="R31" t="n">
+        <v>0.1541138450754072</v>
+      </c>
+      <c r="S31" t="n">
         <v>0.1541138450754073</v>
       </c>
     </row>
@@ -14549,6 +15269,11 @@
           <t>FL</t>
         </is>
       </c>
+      <c r="S34" t="inlineStr">
+        <is>
+          <t>FedAvg</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -14605,6 +15330,9 @@
         <v>0.0892173484180262</v>
       </c>
       <c r="R35" t="n">
+        <v>0.09294821799887509</v>
+      </c>
+      <c r="S35" t="n">
         <v>0.1009969753035638</v>
       </c>
     </row>
@@ -14663,6 +15391,9 @@
         <v>-0.1215319263372537</v>
       </c>
       <c r="R36" t="n">
+        <v>-0.1166439771935841</v>
+      </c>
+      <c r="S36" t="n">
         <v>-0.1085952198888954</v>
       </c>
     </row>
@@ -14721,6 +15452,9 @@
         <v>0.2684375751294062</v>
       </c>
       <c r="R37" t="n">
+        <v>0.2718231556752956</v>
+      </c>
+      <c r="S37" t="n">
         <v>0.2798719129799846</v>
       </c>
     </row>
@@ -14779,6 +15513,9 @@
         <v>0.17922022671138</v>
       </c>
       <c r="R38" t="n">
+        <v>0.1788749376764205</v>
+      </c>
+      <c r="S38" t="n">
         <v>0.1788749376764208</v>
       </c>
     </row>
@@ -14839,6 +15576,9 @@
       <c r="R39" t="n">
         <v>0.2095921951924592</v>
       </c>
+      <c r="S39" t="n">
+        <v>0.2095921951924592</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -14938,6 +15678,11 @@
           <t>FL</t>
         </is>
       </c>
+      <c r="S42" t="inlineStr">
+        <is>
+          <t>FedAvg</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -14994,6 +15739,9 @@
         <v>0.1950901172125922</v>
       </c>
       <c r="R43" t="n">
+        <v>0.2018140053855149</v>
+      </c>
+      <c r="S43" t="n">
         <v>0.2081159145425815</v>
       </c>
     </row>
@@ -15052,6 +15800,9 @@
         <v>-0.026791781259504</v>
       </c>
       <c r="R44" t="n">
+        <v>-0.0198260432242325</v>
+      </c>
+      <c r="S44" t="n">
         <v>-0.0135241340671659</v>
       </c>
     </row>
@@ -15110,6 +15861,9 @@
         <v>0.3926541663001087</v>
       </c>
       <c r="R45" t="n">
+        <v>0.399406307852623</v>
+      </c>
+      <c r="S45" t="n">
         <v>0.4057082170096951</v>
       </c>
     </row>
@@ -15168,6 +15922,9 @@
         <v>0.1975640490875165</v>
       </c>
       <c r="R46" t="n">
+        <v>0.1975923024671081</v>
+      </c>
+      <c r="S46" t="n">
         <v>0.1975923024671136</v>
       </c>
     </row>
@@ -15228,6 +15985,9 @@
       <c r="R47" t="n">
         <v>0.2216400486097474</v>
       </c>
+      <c r="S47" t="n">
+        <v>0.2216400486097474</v>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -15327,6 +16087,11 @@
           <t>FL</t>
         </is>
       </c>
+      <c r="S50" t="inlineStr">
+        <is>
+          <t>FedAvg</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -15383,6 +16148,9 @@
         <v>0.0123829781954728</v>
       </c>
       <c r="R51" t="n">
+        <v>0.0104715609672741</v>
+      </c>
+      <c r="S51" t="n">
         <v>0.015635051485453</v>
       </c>
     </row>
@@ -15441,6 +16209,9 @@
         <v>-0.1593267326654382</v>
       </c>
       <c r="R52" t="n">
+        <v>-0.1615279085760529</v>
+      </c>
+      <c r="S52" t="n">
         <v>-0.156364418057874</v>
       </c>
     </row>
@@ -15499,6 +16270,9 @@
         <v>0.1555672553665316</v>
       </c>
       <c r="R53" t="n">
+        <v>0.1537066829805873</v>
+      </c>
+      <c r="S53" t="n">
         <v>0.1588701734987664</v>
       </c>
     </row>
@@ -15557,6 +16331,9 @@
         <v>0.1431842771710588</v>
       </c>
       <c r="R54" t="n">
+        <v>0.1432351220133132</v>
+      </c>
+      <c r="S54" t="n">
         <v>0.1432351220133134</v>
       </c>
     </row>
@@ -15617,6 +16394,9 @@
       <c r="R55" t="n">
         <v>0.171999469543327</v>
       </c>
+      <c r="S55" t="n">
+        <v>0.171999469543327</v>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -15716,6 +16496,11 @@
           <t>FL</t>
         </is>
       </c>
+      <c r="S58" t="inlineStr">
+        <is>
+          <t>FedAvg</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -15772,6 +16557,9 @@
         <v>-0.2537988317770365</v>
       </c>
       <c r="R59" t="n">
+        <v>-0.2492630203145804</v>
+      </c>
+      <c r="S59" t="n">
         <v>-0.2422983602243206</v>
       </c>
     </row>
@@ -15830,6 +16618,9 @@
         <v>-0.4063906428714465</v>
       </c>
       <c r="R60" t="n">
+        <v>-0.4017951627287828</v>
+      </c>
+      <c r="S60" t="n">
         <v>-0.3948305026385282</v>
       </c>
     </row>
@@ -15888,6 +16679,9 @@
         <v>-0.0975631487987783</v>
       </c>
       <c r="R61" t="n">
+        <v>-0.0934388775641592</v>
+      </c>
+      <c r="S61" t="n">
         <v>-0.0864742174738994</v>
       </c>
     </row>
@@ -15948,6 +16742,9 @@
       <c r="R62" t="n">
         <v>0.1558241427504212</v>
       </c>
+      <c r="S62" t="n">
+        <v>0.1558241427504212</v>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -16004,6 +16801,9 @@
         <v>0.15259181109441</v>
       </c>
       <c r="R63" t="n">
+        <v>0.1525321424142024</v>
+      </c>
+      <c r="S63" t="n">
         <v>0.1525321424142076</v>
       </c>
     </row>
@@ -16105,6 +16905,11 @@
           <t>FL</t>
         </is>
       </c>
+      <c r="S66" t="inlineStr">
+        <is>
+          <t>FedAvg</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -16161,6 +16966,9 @@
         <v>0.0297032937951291</v>
       </c>
       <c r="R67" t="n">
+        <v>0.0280893780472501</v>
+      </c>
+      <c r="S67" t="n">
         <v>0.0354940582195823</v>
       </c>
     </row>
@@ -16219,6 +17027,9 @@
         <v>-0.1226685783463485</v>
       </c>
       <c r="R68" t="n">
+        <v>-0.1240611641719109</v>
+      </c>
+      <c r="S68" t="n">
         <v>-0.1166564839995797</v>
       </c>
     </row>
@@ -16277,6 +17088,9 @@
         <v>0.1708394730732211</v>
       </c>
       <c r="R69" t="n">
+        <v>0.1699024090513999</v>
+      </c>
+      <c r="S69" t="n">
         <v>0.177307089223731</v>
       </c>
     </row>
@@ -16335,6 +17149,9 @@
         <v>0.141136179278092</v>
       </c>
       <c r="R70" t="n">
+        <v>0.1418130310041498</v>
+      </c>
+      <c r="S70" t="n">
         <v>0.1418130310041487</v>
       </c>
     </row>
@@ -16393,6 +17210,9 @@
         <v>0.1523718721414776</v>
       </c>
       <c r="R71" t="n">
+        <v>0.152150542219161</v>
+      </c>
+      <c r="S71" t="n">
         <v>0.152150542219162</v>
       </c>
     </row>
@@ -16494,6 +17314,11 @@
           <t>FL</t>
         </is>
       </c>
+      <c r="S74" t="inlineStr">
+        <is>
+          <t>FedAvg</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -16550,6 +17375,9 @@
         <v>-0.1600473330657868</v>
       </c>
       <c r="R75" t="n">
+        <v>-0.1616326496800893</v>
+      </c>
+      <c r="S75" t="n">
         <v>-0.1632264847820225</v>
       </c>
     </row>
@@ -16608,6 +17436,9 @@
         <v>-0.4140459962497705</v>
       </c>
       <c r="R76" t="n">
+        <v>-0.4163731165652319</v>
+      </c>
+      <c r="S76" t="n">
         <v>-0.417966951667162</v>
       </c>
     </row>
@@ -16666,6 +17497,9 @@
         <v>0.0493797252127198</v>
       </c>
       <c r="R77" t="n">
+        <v>0.047956065778097</v>
+      </c>
+      <c r="S77" t="n">
         <v>0.0463622306761595</v>
       </c>
     </row>
@@ -16724,6 +17558,9 @@
         <v>0.2094270582785066</v>
       </c>
       <c r="R78" t="n">
+        <v>0.2095887154581863</v>
+      </c>
+      <c r="S78" t="n">
         <v>0.209588715458182</v>
       </c>
     </row>
@@ -16782,6 +17619,9 @@
         <v>0.2539986631839837</v>
       </c>
       <c r="R79" t="n">
+        <v>0.2547404668851426</v>
+      </c>
+      <c r="S79" t="n">
         <v>0.2547404668851395</v>
       </c>
     </row>
@@ -16883,6 +17723,11 @@
           <t>FL</t>
         </is>
       </c>
+      <c r="S82" t="inlineStr">
+        <is>
+          <t>FedAvg</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -16939,6 +17784,9 @@
         <v>0.0922246367169947</v>
       </c>
       <c r="R83" t="n">
+        <v>0.09299567437864061</v>
+      </c>
+      <c r="S83" t="n">
         <v>0.0993661300527173</v>
       </c>
     </row>
@@ -16997,6 +17845,9 @@
         <v>-0.07131609911338729</v>
       </c>
       <c r="R84" t="n">
+        <v>-0.07017596536741511</v>
+      </c>
+      <c r="S84" t="n">
         <v>-0.06380550969346641</v>
       </c>
     </row>
@@ -17055,6 +17906,9 @@
         <v>0.2489924077901073</v>
       </c>
       <c r="R85" t="n">
+        <v>0.2506563368447382</v>
+      </c>
+      <c r="S85" t="n">
         <v>0.2570267925188148</v>
       </c>
     </row>
@@ -17113,6 +17967,9 @@
         <v>0.1567677710731126</v>
       </c>
       <c r="R86" t="n">
+        <v>0.1576606624660976</v>
+      </c>
+      <c r="S86" t="n">
         <v>0.1576606624660975</v>
       </c>
     </row>
@@ -17171,6 +18028,9 @@
         <v>0.163540735830382</v>
       </c>
       <c r="R87" t="n">
+        <v>0.1631716397460557</v>
+      </c>
+      <c r="S87" t="n">
         <v>0.1631716397461837</v>
       </c>
     </row>
@@ -17272,6 +18132,11 @@
           <t>FL</t>
         </is>
       </c>
+      <c r="S90" t="inlineStr">
+        <is>
+          <t>FedAvg</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -17328,6 +18193,9 @@
         <v>-0.1566184513110532</v>
       </c>
       <c r="R91" t="n">
+        <v>-0.1547764125997932</v>
+      </c>
+      <c r="S91" t="n">
         <v>-0.1498039596277481</v>
       </c>
     </row>
@@ -17386,6 +18254,9 @@
         <v>-0.2886107949604292</v>
       </c>
       <c r="R92" t="n">
+        <v>-0.286082017000028</v>
+      </c>
+      <c r="S92" t="n">
         <v>-0.281109564027983</v>
       </c>
     </row>
@@ -17444,6 +18315,9 @@
         <v>-0.0337670123816168</v>
       </c>
       <c r="R93" t="n">
+        <v>-0.0327506654617308</v>
+      </c>
+      <c r="S93" t="n">
         <v>-0.027778212489686</v>
       </c>
     </row>
@@ -17502,6 +18376,9 @@
         <v>0.1228514389294364</v>
       </c>
       <c r="R94" t="n">
+        <v>0.1220257471380624</v>
+      </c>
+      <c r="S94" t="n">
         <v>0.1220257471380621</v>
       </c>
     </row>
@@ -17560,6 +18437,9 @@
         <v>0.131992343649376</v>
       </c>
       <c r="R95" t="n">
+        <v>0.1313056044002348</v>
+      </c>
+      <c r="S95" t="n">
         <v>0.1313056044002349</v>
       </c>
     </row>
@@ -17661,6 +18541,11 @@
           <t>FL</t>
         </is>
       </c>
+      <c r="S98" t="inlineStr">
+        <is>
+          <t>FedAvg</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -17717,6 +18602,9 @@
         <v>-0.2478361595517057</v>
       </c>
       <c r="R99" t="n">
+        <v>-0.2471307462982194</v>
+      </c>
+      <c r="S99" t="n">
         <v>-0.2481797356558503</v>
       </c>
     </row>
@@ -17775,6 +18663,9 @@
         <v>-0.4533824864102755</v>
       </c>
       <c r="R100" t="n">
+        <v>-0.4532610112607922</v>
+      </c>
+      <c r="S100" t="n">
         <v>-0.4543100006184232</v>
       </c>
     </row>
@@ -17833,6 +18724,9 @@
         <v>-0.07383332082886131</v>
       </c>
       <c r="R101" t="n">
+        <v>-0.0724960593863305</v>
+      </c>
+      <c r="S101" t="n">
         <v>-0.0735450487439613</v>
       </c>
     </row>
@@ -17891,6 +18785,9 @@
         <v>0.1740028387228444</v>
       </c>
       <c r="R102" t="n">
+        <v>0.1746346869118889</v>
+      </c>
+      <c r="S102" t="n">
         <v>0.174634686911889</v>
       </c>
     </row>
@@ -17949,6 +18846,9 @@
         <v>0.2055463268585698</v>
       </c>
       <c r="R103" t="n">
+        <v>0.2061302649625728</v>
+      </c>
+      <c r="S103" t="n">
         <v>0.2061302649625729</v>
       </c>
     </row>
@@ -18050,6 +18950,11 @@
           <t>FL</t>
         </is>
       </c>
+      <c r="S106" t="inlineStr">
+        <is>
+          <t>FedAvg</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -18106,6 +19011,9 @@
         <v>0.1270466981842133</v>
       </c>
       <c r="R107" t="n">
+        <v>0.1274653456979483</v>
+      </c>
+      <c r="S107" t="n">
         <v>0.1346567160753662</v>
       </c>
     </row>
@@ -18164,6 +19072,9 @@
         <v>-0.0137545861407973</v>
       </c>
       <c r="R108" t="n">
+        <v>-0.0130539393423668</v>
+      </c>
+      <c r="S108" t="n">
         <v>-0.005862568964949</v>
       </c>
     </row>
@@ -18222,6 +19133,9 @@
         <v>0.2595074912872748</v>
       </c>
       <c r="R109" t="n">
+        <v>0.2595909074913602</v>
+      </c>
+      <c r="S109" t="n">
         <v>0.2667822778687781</v>
       </c>
     </row>
@@ -18282,6 +19196,9 @@
       <c r="R110" t="n">
         <v>0.1321255617934119</v>
       </c>
+      <c r="S110" t="n">
+        <v>0.1321255617934119</v>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -18338,6 +19255,9 @@
         <v>0.1408012843250106</v>
       </c>
       <c r="R111" t="n">
+        <v>0.1405192850403151</v>
+      </c>
+      <c r="S111" t="n">
         <v>0.1405192850403152</v>
       </c>
     </row>
@@ -18439,6 +19359,11 @@
           <t>FL</t>
         </is>
       </c>
+      <c r="S114" t="inlineStr">
+        <is>
+          <t>FedAvg</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -18495,6 +19420,9 @@
         <v>-0.0792189995209551</v>
       </c>
       <c r="R115" t="n">
+        <v>-0.0807493756359588</v>
+      </c>
+      <c r="S115" t="n">
         <v>-0.0786132274518678</v>
       </c>
     </row>
@@ -18553,6 +19481,9 @@
         <v>-0.2536486556576801</v>
       </c>
       <c r="R116" t="n">
+        <v>-0.2543730343785209</v>
+      </c>
+      <c r="S116" t="n">
         <v>-0.2522368861944299</v>
       </c>
     </row>
@@ -18611,6 +19542,9 @@
         <v>0.0841016021108807</v>
       </c>
       <c r="R117" t="n">
+        <v>0.0824786533369818</v>
+      </c>
+      <c r="S117" t="n">
         <v>0.08461480152107261</v>
       </c>
     </row>
@@ -18669,6 +19603,9 @@
         <v>0.1633206016318358</v>
       </c>
       <c r="R118" t="n">
+        <v>0.1632280289729406</v>
+      </c>
+      <c r="S118" t="n">
         <v>0.1632280289729404</v>
       </c>
     </row>
@@ -18729,6 +19666,9 @@
       <c r="R119" t="n">
         <v>0.1736236587425621</v>
       </c>
+      <c r="S119" t="n">
+        <v>0.1736236587425621</v>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -18828,6 +19768,11 @@
           <t>FL</t>
         </is>
       </c>
+      <c r="S122" t="inlineStr">
+        <is>
+          <t>FedAvg</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -18884,6 +19829,9 @@
         <v>0.2773478534864938</v>
       </c>
       <c r="R123" t="n">
+        <v>0.2631179013048976</v>
+      </c>
+      <c r="S123" t="n">
         <v>0.26462567840385</v>
       </c>
     </row>
@@ -18942,6 +19890,9 @@
         <v>0.0460666362612896</v>
       </c>
       <c r="R124" t="n">
+        <v>0.03333823791181</v>
+      </c>
+      <c r="S124" t="n">
         <v>0.0348460150107629</v>
       </c>
     </row>
@@ -19000,6 +19951,9 @@
         <v>0.4862734950500242</v>
       </c>
       <c r="R125" t="n">
+        <v>0.4715783283634823</v>
+      </c>
+      <c r="S125" t="n">
         <v>0.4730861054624349</v>
       </c>
     </row>
@@ -19058,6 +20012,9 @@
         <v>0.2089256415635304</v>
       </c>
       <c r="R126" t="n">
+        <v>0.2084604270585847</v>
+      </c>
+      <c r="S126" t="n">
         <v>0.2084604270585849</v>
       </c>
     </row>
@@ -19116,6 +20073,9 @@
         <v>0.2312812172252042</v>
       </c>
       <c r="R127" t="n">
+        <v>0.2297796633930876</v>
+      </c>
+      <c r="S127" t="n">
         <v>0.2297796633930871</v>
       </c>
     </row>
@@ -19130,7 +20090,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R127"/>
+  <dimension ref="A1:S127"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19231,6 +20191,11 @@
           <t>FL</t>
         </is>
       </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>FedAvg</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -19287,6 +20252,9 @@
         <v>0.0075125515835302</v>
       </c>
       <c r="R3" t="n">
+        <v>0.010305624664094</v>
+      </c>
+      <c r="S3" t="n">
         <v>0.1475641189054534</v>
       </c>
     </row>
@@ -19345,6 +20313,9 @@
         <v>-0.1805568798570419</v>
       </c>
       <c r="R4" t="n">
+        <v>-0.1800244730415508</v>
+      </c>
+      <c r="S4" t="n">
         <v>-0.0427659788001829</v>
       </c>
     </row>
@@ -19403,6 +20374,9 @@
         <v>0.1759524426754922</v>
       </c>
       <c r="R5" t="n">
+        <v>0.1852342204658691</v>
+      </c>
+      <c r="S5" t="n">
         <v>0.3224927147072305</v>
       </c>
     </row>
@@ -19461,6 +20435,9 @@
         <v>0.168439891091962</v>
       </c>
       <c r="R6" t="n">
+        <v>0.1749285958017751</v>
+      </c>
+      <c r="S6" t="n">
         <v>0.1749285958017771</v>
       </c>
     </row>
@@ -19519,6 +20496,9 @@
         <v>0.1880694314405721</v>
       </c>
       <c r="R7" t="n">
+        <v>0.1903300977056448</v>
+      </c>
+      <c r="S7" t="n">
         <v>0.1903300977056363</v>
       </c>
     </row>
@@ -19620,6 +20600,11 @@
           <t>FL</t>
         </is>
       </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>FedAvg</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -19676,6 +20661,9 @@
         <v>0.0741316951683027</v>
       </c>
       <c r="R11" t="n">
+        <v>0.0625390636704851</v>
+      </c>
+      <c r="S11" t="n">
         <v>0.1875125556188874</v>
       </c>
     </row>
@@ -19734,6 +20722,9 @@
         <v>-0.076780522798166</v>
       </c>
       <c r="R12" t="n">
+        <v>-0.0904986059377994</v>
+      </c>
+      <c r="S12" t="n">
         <v>0.0344748860107022</v>
       </c>
     </row>
@@ -19792,6 +20783,9 @@
         <v>0.2086253076951914</v>
       </c>
       <c r="R13" t="n">
+        <v>0.2019488133540432</v>
+      </c>
+      <c r="S13" t="n">
         <v>0.3269223053025452</v>
       </c>
     </row>
@@ -19850,6 +20844,9 @@
         <v>0.1344936125268887</v>
       </c>
       <c r="R14" t="n">
+        <v>0.1394097496835581</v>
+      </c>
+      <c r="S14" t="n">
         <v>0.1394097496836578</v>
       </c>
     </row>
@@ -19908,6 +20905,9 @@
         <v>0.1509122179664687</v>
       </c>
       <c r="R15" t="n">
+        <v>0.1530376696082845</v>
+      </c>
+      <c r="S15" t="n">
         <v>0.1530376696081852</v>
       </c>
     </row>
@@ -20009,6 +21009,11 @@
           <t>FL</t>
         </is>
       </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>FedAvg</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -20065,6 +21070,9 @@
         <v>-0.001161955069311</v>
       </c>
       <c r="R19" t="n">
+        <v>-0.0018270491045768</v>
+      </c>
+      <c r="S19" t="n">
         <v>0.188077822414659</v>
       </c>
     </row>
@@ -20123,6 +21131,9 @@
         <v>-0.1811554312556776</v>
       </c>
       <c r="R20" t="n">
+        <v>-0.1854381050308641</v>
+      </c>
+      <c r="S20" t="n">
         <v>0.0044667664883715</v>
       </c>
     </row>
@@ -20181,6 +21192,9 @@
         <v>0.1717942224826119</v>
       </c>
       <c r="R21" t="n">
+        <v>0.1726468647553606</v>
+      </c>
+      <c r="S21" t="n">
         <v>0.3625517362745992</v>
       </c>
     </row>
@@ -20239,6 +21253,9 @@
         <v>0.1729561775519229</v>
       </c>
       <c r="R22" t="n">
+        <v>0.1744739138599374</v>
+      </c>
+      <c r="S22" t="n">
         <v>0.1744739138599402</v>
       </c>
     </row>
@@ -20297,6 +21314,9 @@
         <v>0.1799934761863666</v>
       </c>
       <c r="R23" t="n">
+        <v>0.1836110559262873</v>
+      </c>
+      <c r="S23" t="n">
         <v>0.1836110559262875</v>
       </c>
     </row>
@@ -20398,6 +21418,11 @@
           <t>FL</t>
         </is>
       </c>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>FedAvg</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -20454,6 +21479,9 @@
         <v>0.1464243884039905</v>
       </c>
       <c r="R27" t="n">
+        <v>0.1494733242104051</v>
+      </c>
+      <c r="S27" t="n">
         <v>0.2668178782076981</v>
       </c>
     </row>
@@ -20512,6 +21540,9 @@
         <v>-0.0076826546499477</v>
       </c>
       <c r="R28" t="n">
+        <v>-0.0078548074247134</v>
+      </c>
+      <c r="S28" t="n">
         <v>0.1094897465725794</v>
       </c>
     </row>
@@ -20570,6 +21601,9 @@
         <v>0.2816456082959716</v>
       </c>
       <c r="R29" t="n">
+        <v>0.2897218912719545</v>
+      </c>
+      <c r="S29" t="n">
         <v>0.4070664452693018</v>
       </c>
     </row>
@@ -20628,6 +21662,9 @@
         <v>0.1352212198919811</v>
       </c>
       <c r="R30" t="n">
+        <v>0.1402485670615494</v>
+      </c>
+      <c r="S30" t="n">
         <v>0.1402485670616037</v>
       </c>
     </row>
@@ -20686,6 +21723,9 @@
         <v>0.1541070430539382</v>
       </c>
       <c r="R31" t="n">
+        <v>0.1573281316351185</v>
+      </c>
+      <c r="S31" t="n">
         <v>0.1573281316351187</v>
       </c>
     </row>
@@ -20787,6 +21827,11 @@
           <t>FL</t>
         </is>
       </c>
+      <c r="S34" t="inlineStr">
+        <is>
+          <t>FedAvg</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -20843,6 +21888,9 @@
         <v>0.0881483443753959</v>
       </c>
       <c r="R35" t="n">
+        <v>0.0686574002717556</v>
+      </c>
+      <c r="S35" t="n">
         <v>0.2065307594901419</v>
       </c>
     </row>
@@ -20901,6 +21949,9 @@
         <v>-0.1225660623489675</v>
       </c>
       <c r="R36" t="n">
+        <v>-0.1457699970978819</v>
+      </c>
+      <c r="S36" t="n">
         <v>-0.007896637879246301</v>
       </c>
     </row>
@@ -20959,6 +22010,9 @@
         <v>0.267269553744749</v>
       </c>
       <c r="R37" t="n">
+        <v>0.2511720449364537</v>
+      </c>
+      <c r="S37" t="n">
         <v>0.3890454041551156</v>
       </c>
     </row>
@@ -21017,6 +22071,9 @@
         <v>0.1791212093693531</v>
       </c>
       <c r="R38" t="n">
+        <v>0.1825146446646981</v>
+      </c>
+      <c r="S38" t="n">
         <v>0.1825146446649737</v>
       </c>
     </row>
@@ -21075,6 +22132,9 @@
         <v>0.2107144067243634</v>
       </c>
       <c r="R39" t="n">
+        <v>0.2144273973696375</v>
+      </c>
+      <c r="S39" t="n">
         <v>0.2144273973693882</v>
       </c>
     </row>
@@ -21176,6 +22236,11 @@
           <t>FL</t>
         </is>
       </c>
+      <c r="S42" t="inlineStr">
+        <is>
+          <t>FedAvg</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -21232,6 +22297,9 @@
         <v>0.1948425351437039</v>
       </c>
       <c r="R43" t="n">
+        <v>0.2190041420305547</v>
+      </c>
+      <c r="S43" t="n">
         <v>0.3600366862297288</v>
       </c>
     </row>
@@ -21290,6 +22358,9 @@
         <v>-0.0268735615592343</v>
       </c>
       <c r="R44" t="n">
+        <v>-0.0059528968796822</v>
+      </c>
+      <c r="S44" t="n">
         <v>0.1350796473194883</v>
       </c>
     </row>
@@ -21348,6 +22419,9 @@
         <v>0.3924655382627477</v>
       </c>
       <c r="R45" t="n">
+        <v>0.4211710366601817</v>
+      </c>
+      <c r="S45" t="n">
         <v>0.5622035808593238</v>
       </c>
     </row>
@@ -21406,6 +22480,9 @@
         <v>0.1976230031190438</v>
       </c>
       <c r="R46" t="n">
+        <v>0.202166894629627</v>
+      </c>
+      <c r="S46" t="n">
         <v>0.202166894629595</v>
       </c>
     </row>
@@ -21464,6 +22541,9 @@
         <v>0.2217160967029382</v>
       </c>
       <c r="R47" t="n">
+        <v>0.2249570389102369</v>
+      </c>
+      <c r="S47" t="n">
         <v>0.2249570389102405</v>
       </c>
     </row>
@@ -21565,6 +22645,11 @@
           <t>FL</t>
         </is>
       </c>
+      <c r="S50" t="inlineStr">
+        <is>
+          <t>FedAvg</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -21621,6 +22706,9 @@
         <v>0.0119232488286832</v>
       </c>
       <c r="R51" t="n">
+        <v>0.0072625175169731</v>
+      </c>
+      <c r="S51" t="n">
         <v>0.1290311151495076</v>
       </c>
     </row>
@@ -21679,6 +22767,9 @@
         <v>-0.159753039251414</v>
       </c>
       <c r="R52" t="n">
+        <v>-0.1697252543706537</v>
+      </c>
+      <c r="S52" t="n">
         <v>-0.0479566567381035</v>
       </c>
     </row>
@@ -21737,6 +22828,9 @@
         <v>0.1550355305951876</v>
       </c>
       <c r="R53" t="n">
+        <v>0.1527212957110797</v>
+      </c>
+      <c r="S53" t="n">
         <v>0.2744898933436143</v>
       </c>
     </row>
@@ -21795,6 +22889,9 @@
         <v>0.1431122817665044</v>
       </c>
       <c r="R54" t="n">
+        <v>0.1454587781941066</v>
+      </c>
+      <c r="S54" t="n">
         <v>0.1454587781941067</v>
       </c>
     </row>
@@ -21853,6 +22950,9 @@
         <v>0.1716762880800972</v>
       </c>
       <c r="R55" t="n">
+        <v>0.1769877718876268</v>
+      </c>
+      <c r="S55" t="n">
         <v>0.1769877718876111</v>
       </c>
     </row>
@@ -21954,6 +23054,11 @@
           <t>FL</t>
         </is>
       </c>
+      <c r="S58" t="inlineStr">
+        <is>
+          <t>FedAvg</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -22010,6 +23115,9 @@
         <v>-0.2544186490121233</v>
       </c>
       <c r="R59" t="n">
+        <v>-0.2817238063268104</v>
+      </c>
+      <c r="S59" t="n">
         <v>-0.1912687471963167</v>
       </c>
     </row>
@@ -22068,6 +23176,9 @@
         <v>-0.406895409662136</v>
       </c>
       <c r="R60" t="n">
+        <v>-0.4370862691064479</v>
+      </c>
+      <c r="S60" t="n">
         <v>-0.346631209975998</v>
       </c>
     </row>
@@ -22126,6 +23237,9 @@
         <v>-0.0983063387543239</v>
       </c>
       <c r="R61" t="n">
+        <v>-0.1239998035593101</v>
+      </c>
+      <c r="S61" t="n">
         <v>-0.0335447444288158</v>
       </c>
     </row>
@@ -22184,6 +23298,9 @@
         <v>0.1561123102577994</v>
       </c>
       <c r="R62" t="n">
+        <v>0.1577240027675003</v>
+      </c>
+      <c r="S62" t="n">
         <v>0.1577240027675009</v>
       </c>
     </row>
@@ -22242,6 +23359,9 @@
         <v>0.1524767606500127</v>
       </c>
       <c r="R63" t="n">
+        <v>0.1553624627796375</v>
+      </c>
+      <c r="S63" t="n">
         <v>0.1553624627796813</v>
       </c>
     </row>
@@ -22343,6 +23463,11 @@
           <t>FL</t>
         </is>
       </c>
+      <c r="S66" t="inlineStr">
+        <is>
+          <t>FedAvg</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -22399,6 +23524,9 @@
         <v>0.0294761748958258</v>
       </c>
       <c r="R67" t="n">
+        <v>0.0263769607109096</v>
+      </c>
+      <c r="S67" t="n">
         <v>0.144156538574241</v>
       </c>
     </row>
@@ -22457,6 +23585,9 @@
         <v>-0.12287579469074</v>
       </c>
       <c r="R68" t="n">
+        <v>-0.1281496544327361</v>
+      </c>
+      <c r="S68" t="n">
         <v>-0.0103700765694046</v>
       </c>
     </row>
@@ -22515,6 +23646,9 @@
         <v>0.1705786187973233</v>
       </c>
       <c r="R69" t="n">
+        <v>0.168654189481331</v>
+      </c>
+      <c r="S69" t="n">
         <v>0.2864337673446626</v>
       </c>
     </row>
@@ -22573,6 +23707,9 @@
         <v>0.1411024439014975</v>
       </c>
       <c r="R70" t="n">
+        <v>0.1422772287704214</v>
+      </c>
+      <c r="S70" t="n">
         <v>0.1422772287704216</v>
       </c>
     </row>
@@ -22631,6 +23768,9 @@
         <v>0.1523519695865658</v>
       </c>
       <c r="R71" t="n">
+        <v>0.1545266151436457</v>
+      </c>
+      <c r="S71" t="n">
         <v>0.1545266151436456</v>
       </c>
     </row>
@@ -22732,6 +23872,11 @@
           <t>FL</t>
         </is>
       </c>
+      <c r="S74" t="inlineStr">
+        <is>
+          <t>FedAvg</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -22788,6 +23933,9 @@
         <v>-0.160586697751201</v>
       </c>
       <c r="R75" t="n">
+        <v>-0.1324054666970897</v>
+      </c>
+      <c r="S75" t="n">
         <v>0.0037244727438736</v>
       </c>
     </row>
@@ -22846,6 +23994,9 @@
         <v>-0.4145453796734934</v>
       </c>
       <c r="R76" t="n">
+        <v>-0.3835016647921865</v>
+      </c>
+      <c r="S76" t="n">
         <v>-0.2473717253512375</v>
       </c>
     </row>
@@ -22904,6 +24055,9 @@
         <v>0.0488523801331037</v>
       </c>
       <c r="R77" t="n">
+        <v>0.07912676413845809</v>
+      </c>
+      <c r="S77" t="n">
         <v>0.2152567035794214</v>
       </c>
     </row>
@@ -22964,6 +24118,9 @@
       <c r="R78" t="n">
         <v>0.2115322308355478</v>
       </c>
+      <c r="S78" t="n">
+        <v>0.2115322308355478</v>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -23020,6 +24177,9 @@
         <v>0.2539586819222924</v>
       </c>
       <c r="R79" t="n">
+        <v>0.2510961980950968</v>
+      </c>
+      <c r="S79" t="n">
         <v>0.2510961980951111</v>
       </c>
     </row>
@@ -23121,6 +24281,11 @@
           <t>FL</t>
         </is>
       </c>
+      <c r="S82" t="inlineStr">
+        <is>
+          <t>FedAvg</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -23177,6 +24342,9 @@
         <v>0.0922636106780995</v>
       </c>
       <c r="R83" t="n">
+        <v>0.097583447567269</v>
+      </c>
+      <c r="S83" t="n">
         <v>0.2785717924413751</v>
       </c>
     </row>
@@ -23235,6 +24403,9 @@
         <v>-0.0712624830085454</v>
       </c>
       <c r="R84" t="n">
+        <v>-0.0663952689974697</v>
+      </c>
+      <c r="S84" t="n">
         <v>0.1145930758764899</v>
       </c>
     </row>
@@ -23293,6 +24464,9 @@
         <v>0.2488766197927191</v>
       </c>
       <c r="R85" t="n">
+        <v>0.2579104783891321</v>
+      </c>
+      <c r="S85" t="n">
         <v>0.4388988232634455</v>
       </c>
     </row>
@@ -23351,6 +24525,9 @@
         <v>0.1566130091146196</v>
       </c>
       <c r="R86" t="n">
+        <v>0.1603270308218631</v>
+      </c>
+      <c r="S86" t="n">
         <v>0.1603270308220704</v>
       </c>
     </row>
@@ -23409,6 +24586,9 @@
         <v>0.1635260936866449</v>
       </c>
       <c r="R87" t="n">
+        <v>0.1639787165647387</v>
+      </c>
+      <c r="S87" t="n">
         <v>0.1639787165648852</v>
       </c>
     </row>
@@ -23510,6 +24690,11 @@
           <t>FL</t>
         </is>
       </c>
+      <c r="S90" t="inlineStr">
+        <is>
+          <t>FedAvg</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -23566,6 +24751,9 @@
         <v>-0.1566376648270031</v>
       </c>
       <c r="R91" t="n">
+        <v>-0.1726077181014137</v>
+      </c>
+      <c r="S91" t="n">
         <v>-0.1596409316822981</v>
       </c>
     </row>
@@ -23624,6 +24812,9 @@
         <v>-0.2886036685420726</v>
       </c>
       <c r="R92" t="n">
+        <v>-0.310296454793196</v>
+      </c>
+      <c r="S92" t="n">
         <v>-0.2973296683740804</v>
       </c>
     </row>
@@ -23682,6 +24873,9 @@
         <v>-0.0338222361205194</v>
       </c>
       <c r="R93" t="n">
+        <v>-0.0391834586885799</v>
+      </c>
+      <c r="S93" t="n">
         <v>-0.0262166722694657</v>
       </c>
     </row>
@@ -23740,6 +24934,9 @@
         <v>0.1228154287064837</v>
       </c>
       <c r="R94" t="n">
+        <v>0.1334242594128338</v>
+      </c>
+      <c r="S94" t="n">
         <v>0.1334242594128324</v>
       </c>
     </row>
@@ -23800,6 +24997,9 @@
       <c r="R95" t="n">
         <v>0.1376887366917823</v>
       </c>
+      <c r="S95" t="n">
+        <v>0.1376887366917823</v>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -23899,6 +25099,11 @@
           <t>FL</t>
         </is>
       </c>
+      <c r="S98" t="inlineStr">
+        <is>
+          <t>FedAvg</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -23955,6 +25160,9 @@
         <v>-0.2475810474682927</v>
       </c>
       <c r="R99" t="n">
+        <v>-0.2658065404816105</v>
+      </c>
+      <c r="S99" t="n">
         <v>-0.1407952066275988</v>
       </c>
     </row>
@@ -24013,6 +25221,9 @@
         <v>-0.453124739001827</v>
       </c>
       <c r="R100" t="n">
+        <v>-0.4718070310285675</v>
+      </c>
+      <c r="S100" t="n">
         <v>-0.3467956971745485</v>
       </c>
     </row>
@@ -24071,6 +25282,9 @@
         <v>-0.0736592447917236</v>
       </c>
       <c r="R101" t="n">
+        <v>-0.0885415916152672</v>
+      </c>
+      <c r="S101" t="n">
         <v>0.0364697422387471</v>
       </c>
     </row>
@@ -24129,6 +25343,9 @@
         <v>0.1739218026765691</v>
       </c>
       <c r="R102" t="n">
+        <v>0.1772649488663433</v>
+      </c>
+      <c r="S102" t="n">
         <v>0.1772649488663459</v>
       </c>
     </row>
@@ -24187,6 +25404,9 @@
         <v>0.2055436915335343</v>
       </c>
       <c r="R103" t="n">
+        <v>0.206000490546957</v>
+      </c>
+      <c r="S103" t="n">
         <v>0.2060004905469497</v>
       </c>
     </row>
@@ -24288,6 +25508,11 @@
           <t>FL</t>
         </is>
       </c>
+      <c r="S106" t="inlineStr">
+        <is>
+          <t>FedAvg</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -24344,6 +25569,9 @@
         <v>0.1268448693101463</v>
       </c>
       <c r="R107" t="n">
+        <v>0.1338436137648032</v>
+      </c>
+      <c r="S107" t="n">
         <v>0.2946889659407165</v>
       </c>
     </row>
@@ -24402,6 +25630,9 @@
         <v>-0.0141457001940469</v>
       </c>
       <c r="R108" t="n">
+        <v>-0.0087099719219294</v>
+      </c>
+      <c r="S108" t="n">
         <v>0.1521353802539836</v>
       </c>
     </row>
@@ -24460,6 +25691,9 @@
         <v>0.2592413790844383</v>
       </c>
       <c r="R109" t="n">
+        <v>0.2699717851739064</v>
+      </c>
+      <c r="S109" t="n">
         <v>0.4308171373499366</v>
       </c>
     </row>
@@ -24518,6 +25752,9 @@
         <v>0.132396509774292</v>
       </c>
       <c r="R110" t="n">
+        <v>0.1361281714091032</v>
+      </c>
+      <c r="S110" t="n">
         <v>0.1361281714092201</v>
       </c>
     </row>
@@ -24576,6 +25813,9 @@
         <v>0.1409905695041932</v>
       </c>
       <c r="R111" t="n">
+        <v>0.1425535856867326</v>
+      </c>
+      <c r="S111" t="n">
         <v>0.1425535856867329</v>
       </c>
     </row>
@@ -24677,6 +25917,11 @@
           <t>FL</t>
         </is>
       </c>
+      <c r="S114" t="inlineStr">
+        <is>
+          <t>FedAvg</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -24733,6 +25978,9 @@
         <v>-0.0794222327910523</v>
       </c>
       <c r="R115" t="n">
+        <v>-0.0686989839453733</v>
+      </c>
+      <c r="S115" t="n">
         <v>-0.0041009472404527</v>
       </c>
     </row>
@@ -24791,6 +26039,9 @@
         <v>-0.2538951147395326</v>
       </c>
       <c r="R116" t="n">
+        <v>-0.2452984217129588</v>
+      </c>
+      <c r="S116" t="n">
         <v>-0.1807003850077501</v>
       </c>
     </row>
@@ -24849,6 +26100,9 @@
         <v>0.0838080660317901</v>
       </c>
       <c r="R117" t="n">
+        <v>0.0966210197903523</v>
+      </c>
+      <c r="S117" t="n">
         <v>0.1612190564955611</v>
       </c>
     </row>
@@ -24907,6 +26161,9 @@
         <v>0.1632302988228424</v>
       </c>
       <c r="R118" t="n">
+        <v>0.1653200037357256</v>
+      </c>
+      <c r="S118" t="n">
         <v>0.1653200037360138</v>
       </c>
     </row>
@@ -24965,6 +26222,9 @@
         <v>0.1744728819484803</v>
       </c>
       <c r="R119" t="n">
+        <v>0.1765994377675855</v>
+      </c>
+      <c r="S119" t="n">
         <v>0.1765994377672974</v>
       </c>
     </row>
@@ -25066,6 +26326,11 @@
           <t>FL</t>
         </is>
       </c>
+      <c r="S122" t="inlineStr">
+        <is>
+          <t>FedAvg</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -25122,6 +26387,9 @@
         <v>0.2763760267026727</v>
       </c>
       <c r="R123" t="n">
+        <v>0.2842877306925415</v>
+      </c>
+      <c r="S123" t="n">
         <v>0.3977398959336357</v>
       </c>
     </row>
@@ -25180,6 +26448,9 @@
         <v>0.0451341791062791</v>
       </c>
       <c r="R124" t="n">
+        <v>0.0517697569543745</v>
+      </c>
+      <c r="S124" t="n">
         <v>0.1652219221953278</v>
       </c>
     </row>
@@ -25238,6 +26509,9 @@
         <v>0.4853314168863998</v>
       </c>
       <c r="R125" t="n">
+        <v>0.4941909094678096</v>
+      </c>
+      <c r="S125" t="n">
         <v>0.6076430747087979</v>
       </c>
     </row>
@@ -25296,6 +26570,9 @@
         <v>0.2089553901837271</v>
       </c>
       <c r="R126" t="n">
+        <v>0.2099031787752681</v>
+      </c>
+      <c r="S126" t="n">
         <v>0.2099031787751622</v>
       </c>
     </row>
@@ -25354,6 +26631,9 @@
         <v>0.2312418475963936</v>
       </c>
       <c r="R127" t="n">
+        <v>0.232517973738167</v>
+      </c>
+      <c r="S127" t="n">
         <v>0.2325179737383079</v>
       </c>
     </row>
